--- a/03_synthesis/strava_brainstorm.xlsx
+++ b/03_synthesis/strava_brainstorm.xlsx
@@ -11,9 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📊 TL;DR" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📈 Кластери" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏢 Apps Readout" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️ Коментарі" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Детальні скори" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Інструкція" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📊 Apps Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️ Коментарі" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Детальні скори" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Інструкція" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="167" formatCode="0.00&quot;M&quot;"/>
     <numFmt numFmtId="168" formatCode="&quot;$&quot;0.00&quot;M&quot;"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="46">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -285,8 +286,29 @@
       <color rgb="003B1F5C"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="31">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -447,6 +469,48 @@
         <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+        <bgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A237E"/>
+        <bgColor rgb="001A237E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0037474F"/>
+        <bgColor rgb="0037474F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00263238"/>
+        <bgColor rgb="00263238"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+        <bgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -607,7 +671,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1019,6 +1083,104 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="31" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="31" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="31" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="24" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="31" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="37" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="37" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="37" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="37" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1306,7 +1468,7 @@
       </c>
       <c r="B3" s="78" t="inlineStr">
         <is>
-          <t>Ідея / сегмент</t>
+          <t>Ідея / сегмент + опис</t>
         </is>
       </c>
       <c r="C3" s="78" t="inlineStr">
@@ -1322,12 +1484,6 @@
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>Аргументація (📊 аналітика · 🎓 Genesis · 💬 ментор · 🏁 конкуренти)</t>
-        </is>
-      </c>
-      <c r="F3" s="71" t="inlineStr">
-        <is>
-          <t>🔍 Expansion чи фіча · 🎯 Що зробити далі
-(тільки для L=4-5)</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1498,10 @@
       <c r="A5" s="122" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="123" t="inlineStr">
+      <c r="B5" s="162" t="inlineStr">
         <is>
           <t>Strava Escapes / Active Travel
-Активні мандрівники</t>
+Strava як сервіс для активних подорожей: маршрути в новому місті, готові плани поїздок, локальні клуби і партнерські бронювання.</t>
         </is>
       </c>
       <c r="C5" s="124" t="n">
@@ -1356,33 +1512,12 @@
           <t>✅ KEEP — #1 shortlist</t>
         </is>
       </c>
-      <c r="E5" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА (Paid_Tools_Synthesis §6, 19 Apr 2026)
-Outdoor/Travel кластер Apr'25→'26: 91.7M DL · $326.6M Rev · YoY DL +37.7%.
-AllTrails: 15.7M DL / $76.0M · komoot: 8.1M DL / $35.3M · Wikiloc: 4.5M DL / $9.7M.
-→ Найчистіша валідація в усьому датасеті лектора.
-🎓 GENESIS FRAMEWORK (§2 + §9)
-Market L+growing · Demand Clear · Fit Strong (Heatmaps+Routes — native)
-$ Clear · Proto Medium · Evidence Strong.
-→ 6/6 блоків зелено; проходить правило "right to win &gt; TAM".
-💬 МЕНТОР (19 Apr 2026)
-«Не побачив у вас опції з е-комом тут.» → додати gear-store/партнерства в expansion story.
-🧪 AI-RESEARCH: top-1 у Codex (4.55), top-2 у ChatGPT/Perplexity.
-🏁 КОНКУРЕНТИ: komoot · AllTrails · Wikiloc · Outdooractive · GetYourGuide</t>
-        </is>
-      </c>
-      <c r="F5" s="143" t="inlineStr">
-        <is>
-          <t>🔍 EXPANSION vs ФІЧА
-Strava має: Heatmaps, Routes, Segments, Clubs, offline-maps для tracking.
-Strava НЕ має: destination-first planning (від міста, не від сегмента), multi-day itineraries, bookable guided experiences, paid trail content (AllTrails Pro $76M), e-commerce gear/партнерства (прямий flag ментора).
-→ ПРАВИЛО: Strava Escapes — окремий product surface «плануй→бронюй→купуй», не upgrade Routes.
-🎯 ЩО ЗРОБИТИ ДАЛІ
-1. Teardown komoot Premium + AllTrails+ paid tiers — що саме монетизують.
-2. Mock-концепт «Escapes destination» з bookable element + gear-CTA.
-3. Ahrefs: «hiking trip planner» / «cycling route Italy» — keyword volume.
-4. KILL-criteria: якщо концепт зводиться до «кращі мапи» → swap на Local Exp.</t>
+      <c r="E5" s="163" t="inlineStr">
+        <is>
+          <t>📊 DL 91.7M (+38% YoY) · Rev $326.6M
+AllTrails $76M · komoot $35M · Wikiloc $9.7M
+🎓 Market сильний · Fit сильний · $ доведено
+💬 Ментор: e-commerce gear partnerships як monetization angle</t>
         </is>
       </c>
     </row>
@@ -1390,10 +1525,10 @@
       <c r="A6" s="122" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="123" t="inlineStr">
+      <c r="B6" s="162" t="inlineStr">
         <is>
           <t>Coach Marketplace
-Ті, хто шукає тренера / guided training</t>
+Платформа де юзер знаходить тренера, купує план або супровід, а тренер працює з даними активності прямо через Strava.</t>
         </is>
       </c>
       <c r="C6" s="124" t="n">
@@ -1404,34 +1539,12 @@
           <t>✅ KEEP — #2 shortlist</t>
         </is>
       </c>
-      <c r="E6" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА (Paid_Tools_Synthesis §7)
-Coaching/Training кластер: 7.5M DL · $68.7M Rev · YoY DL +71.4% (!).
-Runna: 6.6M DL / $56.1M (breakout) · TrainingPeaks: 0.36M DL / $7.0M · GOWOD: 0.31M DL / $4.4M.
-→ Найсильніший WTP-сигнал у всьому пакеті даних.
-🎓 GENESIS FRAMEWORK
-Market Medium+hot · Demand Very clear · Fit Strong (Strava вже володіє Runna)
-$ Clear (consumer sub) · Proto Medium · Evidence Strong.
-→ Unique asset: Runna acquisition ⇒ right-to-win наявний з day 1.
-💬 МЕНТОР (19 Apr 2026)
-«Мало хто заробляє, але вигрузку зробив; скачувань теж не у всіх є.»
-→ Datasets підтверджують: монетизація концентрована у 1-2 winners (Runna).
-🧪 AI-RESEARCH: ChatGPT №1 (4.7).
-🏁 КОНКУРЕНТИ: Runna (owned) · TrainingPeaks · Garmin Coach · COROS Training Hub · TrueCoach</t>
-        </is>
-      </c>
-      <c r="F6" s="143" t="inlineStr">
-        <is>
-          <t>🔍 EXPANSION vs ФІЧА
-Strava має: Runna (single-AI-coach → many-athletes), Athlete Intelligence, базові training plans.
-Strava НЕ має: human-coach 2-sided платформи, coach-side tools (TrainingPeaks $7M саме з coach-dashboards!), discovery/matching, supply-economics.
-→ ПРАВИЛО: expansion = 2-sided marketplace з human-coaches. Runna — це product, не marketplace. Не будуємо Runna v2.
-🎯 ЩО ЗРОБИТИ ДАЛІ
-1. Teardown TrainingPeaks coach-side: pricing per-coach, фічі, retention.
-2. Reddit r/running + r/AdvancedRunning: де атлети активно шукають human coaches?
-3. Strava Clubs analysis: скільки клубів мають coaches (supply pool).
-4. KILL-criteria: якщо supply-side gap малий → confirm Runna++, swap на Courts.</t>
+      <c r="E6" s="163" t="inlineStr">
+        <is>
+          <t>📊 DL 7.5M (+71% YoY) · Rev $68.7M
+Runna $56M (breakout) · TrainingPeaks $7M (coach-side!)
+🎓 Найсильніший WTP signal у датасеті · Fit через Runna
+⚠️ Strava вже має Runna — gap: 2-sided human-coach marketplace</t>
         </is>
       </c>
     </row>
@@ -1439,10 +1552,10 @@
       <c r="A7" s="122" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="123" t="inlineStr">
+      <c r="B7" s="162" t="inlineStr">
         <is>
           <t>Local Experiences Marketplace
-Локальні спільноти + мандрівники</t>
+Маркетплейс локальних активностей: пробіжки з local hosts, групові поїздки, хайки, тематичні meetups і платні experience-формати в місті.</t>
         </is>
       </c>
       <c r="C7" s="124" t="n">
@@ -1453,34 +1566,12 @@
           <t>✅ KEEP — #3 shortlist (alt: Courts)</t>
         </is>
       </c>
-      <c r="E7" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА (Paid_Tools_Synthesis §10)
-Events/Travel Discovery: 46.7M DL · $14.1M in-app Rev.
-GetYourGuide 17.5M DL · Fever 11.4M DL · Meetup 4.9M DL / $14.1M · Viator 3.6M DL.
-→ $0 in-app у більшості — значний revenue поза store (booking/GMV).
-🎓 GENESIS FRAMEWORK (§7 Avoid 3: "zero app revenue ≠ weak market")
-Market Large · Demand Clear (adjacent) · Fit Strong (soc graph + location)
-$ Clear (marketplace take-rate) · Proto Medium · Evidence Directional.
-→ Marketplace pattern (§5): matching + liquidity + network effects.
-💬 МЕНТОР
-«Мало ревеню в апках, але багато скачувань, треба прикидувати гроші.»
-→ Ментор підтверджує правило Avoid 3 — рахувати booking-side.
-🧪 AI-RESEARCH: ChatGPT фінальний вибір (4.6).
-🏁 КОНКУРЕНТИ: Meetup · Airbnb Experiences · ClassPass · GetYourGuide · Fever</t>
-        </is>
-      </c>
-      <c r="F7" s="143" t="inlineStr">
-        <is>
-          <t>🔍 EXPANSION vs ФІЧА
-Strava має: soc graph, location data, Clubs (discovery базова).
-Strava НЕ має: marketplace infra (booking, payments, escrow), safety/trust для strangers-meetings, host-tools, take-rate model.
-→ ПРАВИЛО: 100% нова business model (transaction platform). Strava сьогодні = social tracking, не marketplace.
-🎯 ЩО ЗРОБИТИ ДАЛІ (ментор: «прикидувати гроші, а не in-app revenue»)
-1. Teardown Airbnb Experiences + Meetup Pro: take-rates, host onboarding.
-2. Ahrefs: «sunrise run group», «trail run meetup» — real demand volume.
-3. Liquidity-тест: 135M Strava MAU — чи цього достатньо для cold-start?
-4. KILL-criteria: якщо liquidity потребує paid acquisition → swap.</t>
+      <c r="E7" s="163" t="inlineStr">
+        <is>
+          <t>📊 Events/Discovery DL 46.7M · Rev $14M in-app
+GetYourGuide 17.5M DL / $0 in-app · Fever 11.4M / $0 · Meetup $14M
+🎓 §7 Avoid 3: off-app GMV billions — не міряти по in-app
+💬 Ментор: Strava Clubs cold-start без paid acquisition?</t>
         </is>
       </c>
     </row>
@@ -1495,10 +1586,10 @@
       <c r="A9" s="127" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="128" t="inlineStr">
+      <c r="B9" s="164" t="inlineStr">
         <is>
           <t>Strava Live / Race &amp; Event Marketplace
-Атлети + організатори подій</t>
+Маркетплейс забігів і подій: знайти старт, зареєструватись, готуватись у Strava і показати результат у тому ж середовищі.</t>
         </is>
       </c>
       <c r="C9" s="129" t="n">
@@ -1509,30 +1600,12 @@
           <t>🟡 CONSIDER — overlap з #3</t>
         </is>
       </c>
-      <c r="E9" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА
-Events кластер: 46.7M DL · $14.1M Rev (in-app).
-Eventbrite 9.3M DL · Fever 11.4M DL — $0 in-app, бо revenue через reg-fees.
-🎓 GENESIS FRAMEWORK
-Market Medium+growing · Demand Clear · Fit Strong · $ Clear · Proto Medium.
-→ Проходить, АЛЕ overlap з Local Experiences. Можлива merge-ідея.
-💬 МЕНТОР
-«Майже всі не заробляють серед моб-апок — треба дивитися веб. Фрішного SimilarWeb вистачить.»
-🧪 AI-RESEARCH: top-3 у Gemini/ChatGPT/Codex/Perplexity (20-4.4).
-🏁 КОНКУРЕНТИ: RunSignup · Let's Do This · Active.com · Race Roster · Eventbrite</t>
-        </is>
-      </c>
-      <c r="F9" s="143" t="inlineStr">
-        <is>
-          <t>🔍 EXPANSION vs ФІЧА
-Strava має: leaderboards, post-race activity posting, Segments, Challenges.
-Strava НЕ має: registration engine, payment flows, event-organizer tools (RunSignup мова про це), race-day ops, participant-messaging.
-→ ПРАВИЛО: transaction-layer над content. АЛЕ ризик overlap з Local Experiences.
-🎯 ЩО ЗРОБИТИ ДАЛІ (ментор: «фрішного SimilarWeb вистачить»)
-1. SimilarWeb: runsignup.com, letsdothis.com, active.com — traffic + conv rate.
-2. Compare з Local Experiences: overlap &gt;70% → merge в одну ідею.
-3. KILL-criteria: якщо merged варіант виграшніший → абсорбувати у #3.</t>
+      <c r="E9" s="163" t="inlineStr">
+        <is>
+          <t>📊 Events кластер 46.7M DL · $14.1M in-app Rev
+Eventbrite 9.3M DL / $0 · RunSignup web-billing · Meetup $14M
+🎓 Organizer-side economics — ключ (як TrainingPeaks coach-side)
+⚠️ Overlap з #3 (Local Exp) — перевірити merge-сигнал</t>
         </is>
       </c>
     </row>
@@ -1540,10 +1613,10 @@
       <c r="A10" s="127" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="128" t="inlineStr">
+      <c r="B10" s="164" t="inlineStr">
         <is>
           <t>Strava Courts / Social Sports
-Гравці padel / tennis / pickleball</t>
+Розширення у social sports: padel, tennis, pickleball — пошук партнерів, матчі, клуби, рейтинг і потенційно booking court slots.</t>
         </is>
       </c>
       <c r="C10" s="131" t="n">
@@ -1554,87 +1627,58 @@
           <t>🟡 CONSIDER — найкращий swap на #3</t>
         </is>
       </c>
-      <c r="E10" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА (Paid_Tools_Synthesis §8)
-Social Sports/Courts: 4.4M DL · $2.9M Rev · YoY DL +22% (після +40%).
-Playtomic: 3.4M DL / $2.8M (домінує) · CourtReserve: 0.5M / $0 · Pickleheads: 0.2M / $0.04M.
-→ Малий ринок, АЛЕ один з найшвидше-зростаючих кластерів у пакеті.
-🎓 GENESIS FRAMEWORK
-Market Small+fastest · Demand Clear · Fit Medium (Strava запустила Padel Feb'26)
-$ Booking+ecosystem · Proto Easy · Evidence Strong.
-→ Timely non-obvious bet; добре для "differentiated jury story".
-💬 МЕНТОР: (без коментарів)
-🏁 КОНКУРЕНТИ: Playtomic · MATCHi · CourtReserve · Pickleheads</t>
-        </is>
-      </c>
-      <c r="F10" s="144" t="inlineStr"/>
-    </row>
-    <row r="11" ht="26" customHeight="1" s="23">
-      <c r="A11" s="132" t="inlineStr">
+      <c r="E10" s="163" t="inlineStr">
+        <is>
+          <t>📊 DL 4.4M (+22%) · Rev $2.9M in-app (undercount!)
+Playtomic 3.4M DL / $2.8M in-app (real GMV &gt;&gt; app-store)
+🎓 §7 Avoid 3: Playtomic unicorn, $80M+ Series C · fastest-growing cluster
+💬 Ментор: swap-option для Coach Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1" s="23">
+      <c r="A11" s="170" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="174" t="inlineStr">
+        <is>
+          <t>Nutrition / Meal Planning
+Розширення в nutrition layer: meal plans, macro tracking і рекомендації по харчуванню залежно від навантаження та цілей.</t>
+        </is>
+      </c>
+      <c r="C11" s="175" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="174" t="inlineStr">
+        <is>
+          <t>🟡 CONSIDER — ринок масивний ($833M), ментор override</t>
+        </is>
+      </c>
+      <c r="E11" s="176" t="inlineStr">
+        <is>
+          <t>📊 Найбільший revenue-кластер: $833M (+17% YoY)
+MyFitnessPal $382M · Yazio $131M · Cal AI $57M (+172%)
+AI-хвиля: Calo +2850% · BitePal +897% · Rev: $301M→$714M→$833M
+🎓 §2.D Fit weak (dilutes identity) · §2.C crowded
+💬 Ментор: «не викидати з шорт-ліста — хороший ринок по грошах»</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="290" customHeight="1" s="23">
+      <c r="A12" s="132" t="inlineStr">
         <is>
           <t>🟠 DEPRIORITIZE — сильні на перший погляд, але фреймворк блокує</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="290" customHeight="1" s="23">
-      <c r="A12" s="133" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="134" t="inlineStr">
-        <is>
-          <t>Strava Work / Corporate Wellness
-Компанії і HR</t>
-        </is>
-      </c>
-      <c r="C12" s="135" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="59" t="inlineStr">
-        <is>
-          <t>⚠️ DEPRIORITIZE — fail right-to-win</t>
-        </is>
-      </c>
-      <c r="E12" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА (Paid_Tools_Synthesis §3 Comment 4)
-❌ Цим датасетом НЕ валідується.
-B2B revenue поза app-store: Wellhub $315M ARR (est) · Virgin Pulse $400M+ · Limeade acq $175M.
-→ Для валідації потрібні PitchBook / CB Insights / Crunchbase.
-🎓 GENESIS FRAMEWORK — FAIL
-Market Huge TAM · Demand Weak in data · Fit Partial (B2B-sales ≠ DNA Strava)
-$ Long cycle · Proto Hard (HR-dashboards) · Evidence Weak тут.
-→ Прямо порушує §4 Prioritization rule: "не вибирати за TAM".
-Порушує §10 expected output — «main risk" = dilute consumer brand.
-💬 МЕНТОР
-«Тут треба шукати щось про гроші у відкритих джерелах.»
-→ Ментор сам прямо сигналить, що app-store даних бракує.
-🧪 AI-RESEARCH: Всі 6 у топ-3, Gemini/DOCX/Perplexity ставлять №1. Але це judgment AI, не hard evidence.
-🏁 КОНКУРЕНТИ: Wellhub · Virgin Pulse · Limeade · Vitality · BetterMe Business</t>
-        </is>
-      </c>
-      <c r="F12" s="143" t="inlineStr">
-        <is>
-          <t>🔍 EXPANSION vs ФІЧА
-Strava має: Clubs, Challenges, Leaderboards (consumer-side).
-Strava НЕ має: HR-дашборди, SSO/SAML, invoicing, enterprise sales motion, account-managers, compliance (SOC2), admin-controls.
-→ ПРАВИЛО: B2B — це не feature, це інша DNA, інший sales-cycle, інша команда. Саме тому §4 Genesis «не за TAM» спрацьовує.
-🎯 ЩО ЗРОБИТИ ДАЛІ (ментор: «шукати гроші у відкритих джерелах»)
-1. PitchBook/Crunchbase: Wellhub ARR, Virgin Pulse Rev, Limeade acq thesis.
-2. Gympass public filings (post-IPO): margins, CAC, churn, sales-cycle length.
-3. Precedents: чи consumer-brand переходили у B2B успішно (Slack? Notion?).
-4. KILL-criteria (вже тригер): confirm DEPRIORITIZE, не робити deep-dive.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="290" customHeight="1" s="23">
       <c r="A13" s="133" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="134" t="inlineStr">
-        <is>
-          <t>Strava Ready / Recovery &amp; Longevity
-Recovery + sleep</t>
+        <v>6</v>
+      </c>
+      <c r="B13" s="165" t="inlineStr">
+        <is>
+          <t>Strava Work / Corporate Wellness
+Продукт для компаній: командні челенджі, корпоративні клуби, leaderboard-и, адмінка для HR і аналітика залучення працівників.</t>
         </is>
       </c>
       <c r="C13" s="135" t="n">
@@ -1642,44 +1686,26 @@
       </c>
       <c r="D13" s="59" t="inlineStr">
         <is>
-          <t>⚠️ DEPRIORITIZE — феча, не wedge</t>
-        </is>
-      </c>
-      <c r="E13" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА (Paid_Tools_Synthesis §9)
-Recovery/Longevity: 6.2M DL · $0.7M Rev · YoY DL +82.8%.
-Oura 3.4M DL / $0 · WHOOP 2.7M DL / $0 · Eight Sleep 0.03M / $0.6M.
-→ Demand є, але монетизація hardware-led (поза app-store).
-🎓 GENESIS FRAMEWORK
-Market Growing · Demand Partial · Fit Medium · $ Weak in store · Proto Medium · Evidence Mixed.
-→ §7 Avoid 3: нуль in-app — нормально. АЛЕ §7 Avoid 4: це більше feature/retention layer, не expansion wedge.
-💬 МЕНТОР
-«Скачування на апках-конекторах — можна розглядати як проксі до покупки. Як щодо розглянути sleep-apps?»
-🏁 КОНКУРЕНТИ: WHOOP · Oura · Eight Sleep · Garmin Body Battery · HRV4Training</t>
-        </is>
-      </c>
-      <c r="F13" s="143" t="inlineStr">
-        <is>
-          <t>🔍 EXPANSION vs ФІЧА
-Strava має: training load, activity history, TSS.
-Strava НЕ має: HRV-сенсор, sleep-трекінг, recovery-алгоритми, wearable.
-→ ПРАВИЛО: без hardware це тільки software layer → feature на tracking, не новий ринок. Всі winners (Oura/WHOOP) — hardware-led.
-🎯 ЩО ЗРОБИТИ ДАЛІ (ментор: «downloads як proxy, розглянути sleep-apps»)
-1. Teardown Oura vs WHOOP business models: Rev breakdown (hardware vs app)?
-2. Rise Science, Pillow, Sleep Cycle — чи app-only sleep монетизується?
-3. KILL-criteria: якщо всі winners мають hardware → confirm DEPRIORITIZE до «feature layer для premium», зняти з expansion list.</t>
+          <t>⚠️ DEPRIORITIZE — fail right-to-win</t>
+        </is>
+      </c>
+      <c r="E13" s="163" t="inlineStr">
+        <is>
+          <t>📊 ❌ Цим датасетом НЕ валідується (B2B поза app-store)
+Wellhub $315M ARR · Virgin Pulse $400M+ — потрібен PitchBook
+🎓 §2.D Fit weak · Right-to-win questionable проти enterprise HR
+💬 Ментор: без коментарів (не фокус)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="290" customHeight="1" s="23">
       <c r="A14" s="133" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="134" t="inlineStr">
-        <is>
-          <t>Creator Pass / Creator Economy
-Спортивні creator-и</t>
+        <v>7</v>
+      </c>
+      <c r="B14" s="165" t="inlineStr">
+        <is>
+          <t>Strava Ready / Recovery &amp; Longevity
+Шар відновлення: readiness score, ризик перевантаження, поради щодо recovery на базі навантаження й сторонніх health signals.</t>
         </is>
       </c>
       <c r="C14" s="135" t="n">
@@ -1687,45 +1713,26 @@
       </c>
       <c r="D14" s="59" t="inlineStr">
         <is>
-          <t>⚠️ DEPRIORITIZE — monetization extension</t>
-        </is>
-      </c>
-      <c r="E14" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА
-Немає прямого кластера. Адʼяцентний Coaching (Runna $56M).
-Playbook, Fitplan, Ladder — поза top-ревʼю (низькі DL).
-🎓 GENESIS FRAMEWORK — FAIL §7 Avoid 4
-Market Medium · Demand Partial · Fit Strong · $ Unproven · Evidence Weak.
-→ Це monetization layer поверх існуючого продукту, а не new-market expansion, яку вимагає бриф.
-💬 МЕНТОР
-«Ladder — по суті workout-апка, можливо віднести до Coaching. Те саме з Patreon і Peloton — розвести по правильних нішах.»
-→ Ментор сам сигналить про categorization-розпад ідеї.
-🧪 AI-RESEARCH: Gemini top-2 (23/25), але бенчмарк Patreon — analog, не direct.
-🏁 КОНКУРЕНТИ: Playbook · Fitplan · Ladder · Future · Patreon (analog)</t>
-        </is>
-      </c>
-      <c r="F14" s="143" t="inlineStr">
-        <is>
-          <t>🔍 EXPANSION vs ФІЧА
-Strava має: athletes + influencers на платформі, content-posting, social graph.
-Strava НЕ має: monetization splits, creator payout infra, subscription-per-creator.
-→ ПРАВИЛО: це monetization layer поверх Coach або social → не new-market expansion. Ментор прямо вказав на categorization-розпад (Ladder = Coach, Patreon = SaaS).
-🎯 ЩО ЗРОБИТИ ДАЛІ
-1. Re-classify: Ladder → Coach Marketplace; Patreon → аналог не competitor.
-2. Evaluate: чи можна абсорбувати «creator-як-coach» у Coach Marketplace як supply-type?
-3. KILL-criteria (вже тригер): confirm KILL як окрема ідея; absorb у #2.</t>
+          <t>⚠️ DEPRIORITIZE — феча, не wedge</t>
+        </is>
+      </c>
+      <c r="E14" s="163" t="inlineStr">
+        <is>
+          <t>📊 DL 6.2M (+83%) · Rev $0.7M in-app
+Oura 3.4M DL / $0 · WHOOP 2.7M / $0 · Eight Sleep $0.6M
+🎓 Demand є, monetization hardware-led — не app-store
+→ Краще як retention feature, ніж самостійна вертикаль</t>
         </is>
       </c>
     </row>
     <row r="15" ht="290" customHeight="1" s="23">
       <c r="A15" s="133" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="134" t="inlineStr">
-        <is>
-          <t>Club OS / Organizer Tools
-Організатори клубів</t>
+        <v>8</v>
+      </c>
+      <c r="B15" s="165" t="inlineStr">
+        <is>
+          <t>Creator Pass / Creator Economy
+Модель для спортивних creator-ів: платні клуби, challenge series, контент, тренувальні добірки або закриті програми для аудиторії.</t>
         </is>
       </c>
       <c r="C15" s="135" t="n">
@@ -1733,76 +1740,53 @@
       </c>
       <c r="D15" s="59" t="inlineStr">
         <is>
-          <t>⚠️ DEPRIORITIZE — utility layer</t>
-        </is>
-      </c>
-      <c r="E15" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА (Paid_Tools_Synthesis §11)
-Community/Team Ops: 16.5M DL · $4.7M Rev · YoY DL ~flat.
-GroupMe 10.0M DL / $0 · Spond 2.4M / $0 · TeamSnap 1.6M / $3.8M.
-→ Стабільний utility, без вибухового зростання.
-🎓 GENESIS FRAMEWORK — FAIL §7 Avoid 4
-Market Flat · Fit Strong · $ Utility-rev · Evidence Partial.
-→ §11 Bottom line: «не big, не trendy, не easy-to-proto» — цей варіант саме «easy-to-proto», але flat market.
-💬 МЕНТОР
-«Деяких апок не знайшов — можливо web-based. Багато скачувань і не у всіх є ревеню. GroupMe здається сюди не підходить.»
-🏁 КОНКУРЕНТИ: Spond · TeamSnap · BAND · Heja · SportsEngine</t>
-        </is>
-      </c>
-      <c r="F15" s="143" t="inlineStr">
-        <is>
-          <t>🔍 EXPANSION vs ФІЧА
-Strava має: Clubs (базові).
-Strava НЕ має: scheduling, payments, organizer-dashboards, messaging, event-mgmt.
-→ ПРАВИЛО: utility layer на core Clubs — це feature, не expansion. Flat market (Community/Team Ops §11 synthesis). Spond $0 monetization — додатковий сигнал.
-🎯 ЩО ЗРОБИТИ ДАЛІ (ментор: «GroupMe сюди не підходить; багато DL без revenue»)
-1. Teardown Spond: як вони живуть без revenue? VC burn чи freemium?
-2. TeamSnap $3.8M Rev — breakdown: що саме монетизують (premium тір, ads)?
-3. KILL-criteria (вже тригер): confirm DEPRIORITIZE до feature-рівня Strava Clubs.</t>
+          <t>⚠️ DEPRIORITIZE — monetization extension</t>
+        </is>
+      </c>
+      <c r="E15" s="163" t="inlineStr">
+        <is>
+          <t>📊 Немає прямого кластера · Playbook/Fitplan — низькі DL
+🎓 §7 Avoid 4: monetization extension, не expansion
+💬 Ментор: без коментарів
+→ Потенційно як add-on до Coach Marketplace</t>
         </is>
       </c>
     </row>
     <row r="16" ht="160" customHeight="1" s="23">
       <c r="A16" s="133" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="134" t="inlineStr">
-        <is>
-          <t>Return-to-Activity / Pre-Hab
-Після травм</t>
-        </is>
-      </c>
-      <c r="C16" s="136" t="n">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="B16" s="165" t="inlineStr">
+        <is>
+          <t>Club OS / Organizer Tools
+Операційний інструмент для організаторів клубів: анонси, учасники, attendance, recurring events і координація спільноти.</t>
+        </is>
+      </c>
+      <c r="C16" s="135" t="n">
+        <v>4</v>
       </c>
       <c r="D16" s="59" t="inlineStr">
         <is>
-          <t>⚠️ DEPRIORITIZE — regulatory</t>
-        </is>
-      </c>
-      <c r="E16" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА
-Адʼяцентний Coaching-кластер: Runna $56M · GOWOD $4.4M · Recover Athletics $0.1M.
-🎓 GENESIS FRAMEWORK
-Demand Clear · Fit Strong · $ Partial · Proto Hard (medical claims).
-→ §7 Avoid 1 ризик: «idea vs. feature» — можна сприйняти як feature Strava Ready.
-💬 МЕНТОР: (без коментарів)
-🧪 AI: Gemini H8 17/25, Codex 3.55. &gt;50% раннерів мають injury щороку.
-🏁 КОНКУРЕНТИ: GOWOD · Recover Athletics · Runna · Physitrack</t>
-        </is>
-      </c>
-      <c r="F16" s="144" t="inlineStr"/>
+          <t>⚠️ DEPRIORITIZE — utility layer</t>
+        </is>
+      </c>
+      <c r="E16" s="163" t="inlineStr">
+        <is>
+          <t>📊 Community/Team Ops DL 16.5M (flat) · Rev $4.7M
+GroupMe 10M DL / $0 · TeamSnap 1.6M / $3.8M · Spond 2.4M / $0
+🎓 Utility layer — стабільний але не вибуховий ринок
+→ Краще як фіча Clubs, не окрема вертикаль</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="160" customHeight="1" s="23">
       <c r="A17" s="133" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="134" t="inlineStr">
-        <is>
-          <t>Outdoor Group Safety / Beacon+
-Групи на природі</t>
+        <v>10</v>
+      </c>
+      <c r="B17" s="165" t="inlineStr">
+        <is>
+          <t>Return-to-Activity / Pre-Hab
+Продукт для повернення після травм: обережні плани навантаження, контроль прогресії і підказки як не перевантажитись знову.</t>
         </is>
       </c>
       <c r="C17" s="136" t="n">
@@ -1810,98 +1794,84 @@
       </c>
       <c r="D17" s="59" t="inlineStr">
         <is>
-          <t>⚠️ DEPRIORITIZE — дублює Active Travel</t>
-        </is>
-      </c>
-      <c r="E17" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА
-Немає кластерних даних. Garmin inReach — hardware-led.
-🎓 GENESIS FRAMEWORK
-Demand Partial · Fit Strong (Strava Beacon вже є) · $ Weak · Evidence Weak.
-→ §7 Avoid 1: «feature of Active Travel», не окрема ідея.
-💬 МЕНТОР
-«Щось таке вже було з хайкінгом і гіром.» → прямо підтверджує дублювання.
-🏁 КОНКУРЕНТИ: Garmin inReach · SPOT Gen4 · Noonlight · Cairn (AllTrails+)</t>
-        </is>
-      </c>
-      <c r="F17" s="144" t="inlineStr"/>
+          <t>⚠️ DEPRIORITIZE — regulatory</t>
+        </is>
+      </c>
+      <c r="E17" s="163" t="inlineStr">
+        <is>
+          <t>📊 Coaching adj: Runna $56M · GOWOD $4.4M · Recover $0.1M
+🎓 Demand є · Fit сильний · Proto hard (medical claims)
+→ §7 Avoid 1: risk regulatory + liability</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="160" customHeight="1" s="23">
       <c r="A18" s="133" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="165" t="inlineStr">
+        <is>
+          <t>Outdoor Group Safety / Beacon+
+Посилений безпековий режим для групових outdoor-активностей: live location, safety overlays, координація і emergency flows.</t>
+        </is>
+      </c>
+      <c r="C18" s="136" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="59" t="inlineStr">
+        <is>
+          <t>⚠️ DEPRIORITIZE — дублює Active Travel</t>
+        </is>
+      </c>
+      <c r="E18" s="163" t="inlineStr">
+        <is>
+          <t>📊 Немає кластерних даних · Garmin inReach hardware-led
+🎓 Strava Beacon вже існує → це feature extension
+→ §7 Avoid 1: дублює Active Travel safety layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1" s="23">
+      <c r="A19" s="133" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="134" t="inlineStr">
+      <c r="B19" s="165" t="inlineStr">
         <is>
           <t>Gear Recommerce
-Перепродаж спорядження</t>
-        </is>
-      </c>
-      <c r="C18" s="137" t="n">
+Перепродаж спорядження в екосистемі Strava: вживані велосипеди, кросівки, гаджети. Слабший fit із core strengths продукту.</t>
+        </is>
+      </c>
+      <c r="C19" s="137" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="59" t="inlineStr">
+      <c r="D19" s="59" t="inlineStr">
         <is>
           <t>⚠️ DEPRIORITIZE — ops complexity</t>
         </is>
       </c>
-      <c r="E18" s="125" t="inlineStr">
-        <is>
-          <t>📊 АНАЛІТИКА
-Немає в датасеті. Pro's Closet, BuyCycle — nascent.
-🎓 GENESIS FRAMEWORK
-Demand Unknown · Fit Partial · $ Marketplace ops-heavy · Proto Hard.
-→ §5 Marketplace pattern — вимагає liquidity; §9 Final decision rule не виконується.
-💬 МЕНТОР
-«Не дуже релевантні конкуренти — я би дивився search volume на б/у речі.»
-→ Треба переробити competitor set і рахувати keyword demand.
-🏁 КОНКУРЕНТИ: The Pro's Closet · BuyCycle · eBay · Facebook Marketplace · Depop</t>
-        </is>
-      </c>
-      <c r="F18" s="144" t="inlineStr"/>
-    </row>
-    <row r="19" ht="26" customHeight="1" s="23">
-      <c r="A19" s="138" t="inlineStr">
+      <c r="E19" s="163" t="inlineStr">
+        <is>
+          <t>📊 Немає у датасеті · Pro's Closet / BuyCycle nascent
+🎓 Marketplace ops-heavy · Liquidity потрібна · Fit Partial
+→ §5: marketplace pattern — холодний старт дуже важкий</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1" s="23">
+      <c r="A20" s="138" t="inlineStr">
         <is>
           <t>🔴 KILL — зняти з розгляду</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="80" customHeight="1" s="23">
-      <c r="A20" s="139" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="140" t="inlineStr">
-        <is>
-          <t>Guided Audio / Adaptive Beginner Coach
-Новачки</t>
-        </is>
-      </c>
-      <c r="C20" s="141" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="61" t="inlineStr">
-        <is>
-          <t>🚫 KILL — прямі конкуренти</t>
-        </is>
-      </c>
-      <c r="E20" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §7 Avoid 4: Fit конфліктує з endurance-DNA Strava.
-💬 МЕНТОР: «Це просто около-прямі конкуренти Strava (NRC, Runkeeper).»
-🏁 КОНКУРЕНТИ: Nike Run Club (free) · Runkeeper Go · C25K · adidas Running</t>
-        </is>
-      </c>
-      <c r="F20" s="144" t="inlineStr"/>
     </row>
     <row r="21" ht="80" customHeight="1" s="23">
       <c r="A21" s="139" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" s="140" t="inlineStr">
-        <is>
-          <t>University Communities
-Студентські спільноти</t>
+        <v>13</v>
+      </c>
+      <c r="B21" s="168" t="inlineStr">
+        <is>
+          <t>Guided Audio / Adaptive Beginner Coach
+Продукт для новачків: guided audio runs, прості адаптивні плани, м'який onboarding без тиску складної спортивної аналітики.</t>
         </is>
       </c>
       <c r="C21" s="141" t="n">
@@ -1909,27 +1879,25 @@
       </c>
       <c r="D21" s="61" t="inlineStr">
         <is>
-          <t>🚫 KILL — нема монетизації</t>
-        </is>
-      </c>
-      <c r="E21" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §2.E $ weak · §9 Final rule не виконується.
-💬 МЕНТОР (19 Apr): «Нема грошей у студентів.»
-📊 АНАЛІТИКА: Community кластер flat, campus-specific apps не у топ.
-🏁 КОНКУРЕНТИ: Corq · Campus Labs · IMLeagues · Gipper</t>
-        </is>
-      </c>
-      <c r="F21" s="144" t="inlineStr"/>
+          <t>🚫 KILL — прямі конкуренти</t>
+        </is>
+      </c>
+      <c r="E21" s="163" t="inlineStr">
+        <is>
+          <t>🎓 §7 Avoid 4: конкурує з NRC / Runkeeper — direct overlap
+💬 Ментор: «Це просто около-прямі конкуренти Strava»
+🏁 Nike Run Club · Runkeeper · C25K — free dominant</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="80" customHeight="1" s="23">
       <c r="A22" s="139" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="140" t="inlineStr">
-        <is>
-          <t>Family Movement
-Сімʼї</t>
+        <v>14</v>
+      </c>
+      <c r="B22" s="168" t="inlineStr">
+        <is>
+          <t>University Communities
+Campus-версія Strava: спільноти університетів, rivalry між факультетами, студентські клуби й локальні challenge-и.</t>
         </is>
       </c>
       <c r="C22" s="141" t="n">
@@ -1937,27 +1905,25 @@
       </c>
       <c r="D22" s="61" t="inlineStr">
         <is>
-          <t>🚫 KILL — monetization extension</t>
-        </is>
-      </c>
-      <c r="E22" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §7 Avoid 4: це monetization extension, а не expansion.
-💬 МЕНТОР: «Це скоріше розширення монетизації, а не окрема вертикаль.»
-📊 АНАЛІТИКА: Life360 — adjacent; family-fitness niche немає scale-apps.
-🏁 КОНКУРЕНТИ: Life360 · Cozi Family · Goosechase · Apple Family</t>
-        </is>
-      </c>
-      <c r="F22" s="144" t="inlineStr"/>
+          <t>🚫 KILL — нема монетизації</t>
+        </is>
+      </c>
+      <c r="E22" s="163" t="inlineStr">
+        <is>
+          <t>🎓 §2.E $ weak · §9 Final rule не виконується
+💬 Ментор: «Нема грошей у студентів»
+📊 Community кластер flat · campus apps не у топ</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="80" customHeight="1" s="23">
       <c r="A23" s="139" t="n">
-        <v>16</v>
-      </c>
-      <c r="B23" s="140" t="inlineStr">
-        <is>
-          <t>AI Strength Form Coach
-Силові тренування</t>
+        <v>15</v>
+      </c>
+      <c r="B23" s="168" t="inlineStr">
+        <is>
+          <t>Family Movement
+Сімейний формат: спільні активності, household challenge-и, безпечний режим для дітей і мотивація рухатись як сім'я.</t>
         </is>
       </c>
       <c r="C23" s="141" t="n">
@@ -1965,27 +1931,25 @@
       </c>
       <c r="D23" s="61" t="inlineStr">
         <is>
-          <t>🚫 KILL — weak fit, hard proto</t>
-        </is>
-      </c>
-      <c r="E23" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §2.D Fit weak (endurance DNA) · Proto Hard (CV/ML).
-💬 МЕНТОР: «Частину цих апок вже вигрузив.» (neutral)
-📊 АНАЛІТИКА: Tonal/Future — hardware-led, не app-store Rev.
-🏁 КОНКУРЕНТИ: Tonal · Future · Fitbod · JEFIT · Apple Fitness+ Strength</t>
-        </is>
-      </c>
-      <c r="F23" s="144" t="inlineStr"/>
+          <t>🚫 KILL — monetization extension</t>
+        </is>
+      </c>
+      <c r="E23" s="163" t="inlineStr">
+        <is>
+          <t>🎓 §7 Avoid 4: monetization extension, не expansion
+💬 Ментор: «Скоріше розширення монетизації»
+📊 Life360 adjacent · family-fitness niche no scale</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="80" customHeight="1" s="23">
       <c r="A24" s="139" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" s="140" t="inlineStr">
-        <is>
-          <t>Adaptive / Inclusive Fitness
-Люди з інвалідністю</t>
+        <v>16</v>
+      </c>
+      <c r="B24" s="168" t="inlineStr">
+        <is>
+          <t>AI Strength Form Coach
+Силові тренування: записуєш вправу на камеру, отримуєш аналіз техніки, підказки щодо form і відстеження прогресу в lifting.</t>
         </is>
       </c>
       <c r="C24" s="141" t="n">
@@ -1993,55 +1957,51 @@
       </c>
       <c r="D24" s="61" t="inlineStr">
         <is>
-          <t>🚫 KILL — малий ринок</t>
-        </is>
-      </c>
-      <c r="E24" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §2.A Market small · §9 Final rule не виконується.
-💬 МЕНТОР: «Малий ринок.»
-📊 АНАЛІТИКА: Нуль scale-apps у датасеті.
-🏁 КОНКУРЕНТИ: GRIT Freedom Chair · Move United (limited direct)</t>
-        </is>
-      </c>
-      <c r="F24" s="144" t="inlineStr"/>
+          <t>🚫 KILL — weak fit, hard proto</t>
+        </is>
+      </c>
+      <c r="E24" s="163" t="inlineStr">
+        <is>
+          <t>🎓 §2.D Fit weak (endurance DNA) · Proto hard (CV/ML)
+💬 Ментор: «Частину цих апок вже вигрузив» (neutral)
+🏁 Tonal / Future — hardware-led incumbent</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="80" customHeight="1" s="23">
       <c r="A25" s="139" t="n">
-        <v>18</v>
-      </c>
-      <c r="B25" s="140" t="inlineStr">
-        <is>
-          <t>Health-Insurance Subsidy / Proprietary Hardware
-Страхування + власні девайси</t>
-        </is>
-      </c>
-      <c r="C25" s="142" t="n">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="B25" s="168" t="inlineStr">
+        <is>
+          <t>Adaptive / Inclusive Fitness
+Інклюзивні тренування: окремі програми для людей з інвалідністю, prenatal/postnatal і нестандартних fitness-потреб.</t>
+        </is>
+      </c>
+      <c r="C25" s="141" t="n">
+        <v>3</v>
       </c>
       <c r="D25" s="61" t="inlineStr">
         <is>
-          <t>🚫 KILL — tier-1 вже має</t>
-        </is>
-      </c>
-      <c r="E25" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §2.D Fit weak (dilutes DNA) · §2.E regul. complex.
-💬 МЕНТОР: «На tier-1 ринках страхування і так є базове fitness-перекриття.»
-📊 АНАЛІТИКА: Recovery кластер показує hardware-led логіку — тяжко для software-first.
-🏁 КОНКУРЕНТИ: Vitality Health · Dacadoo · UnitedHealthcare Motion</t>
-        </is>
-      </c>
-      <c r="F25" s="144" t="inlineStr"/>
+          <t>🚫 KILL — малий ринок</t>
+        </is>
+      </c>
+      <c r="E25" s="163" t="inlineStr">
+        <is>
+          <t>🎓 §2.A Market small · §9 Final rule fail
+💬 Ментор: «Малий ринок»
+📊 Нуль scale-apps у датасеті</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="80" customHeight="1" s="23">
       <c r="A26" s="139" t="n">
-        <v>19</v>
-      </c>
-      <c r="B26" s="140" t="inlineStr">
-        <is>
-          <t>Fitness Dating
-Знайомства</t>
+        <v>18</v>
+      </c>
+      <c r="B26" s="168" t="inlineStr">
+        <is>
+          <t>Health-Insurance Subsidy / Proprietary Hardware
+Вихід у страхування або власні девайси — великий масштаб і складність, не підходить під короткий горизонт реалізації.</t>
         </is>
       </c>
       <c r="C26" s="142" t="n">
@@ -2049,27 +2009,25 @@
       </c>
       <c r="D26" s="61" t="inlineStr">
         <is>
-          <t>🚫 KILL — ризик для core</t>
-        </is>
-      </c>
-      <c r="E26" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §2.D Risk to core · §7 Avoid: не підходить під DNA.
-💬 МЕНТОР: «Тут питання релевантності задачі та потенційної конверсії.»
-📊 АНАЛІТИКА: Bumble fitness mode — feature, не окремий app.
-🏁 КОНКУРЕНТИ: Bumble (fitness mode) · Datefit · Fitafy · Hinge</t>
-        </is>
-      </c>
-      <c r="F26" s="144" t="inlineStr"/>
+          <t>🚫 KILL — tier-1 вже має</t>
+        </is>
+      </c>
+      <c r="E26" s="163" t="inlineStr">
+        <is>
+          <t>🎓 §2.D Fit weak · §2.E regulatory complex
+💬 Ментор: «Tier-1 ринки — страхування вже є базове coverage»
+→ Too far from Strava core</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="80" customHeight="1" s="23">
       <c r="A27" s="139" t="n">
-        <v>20</v>
-      </c>
-      <c r="B27" s="140" t="inlineStr">
-        <is>
-          <t>Nutrition / Meal Planning
-Харчування</t>
+        <v>19</v>
+      </c>
+      <c r="B27" s="168" t="inlineStr">
+        <is>
+          <t>Fitness Dating
+Знайомства через активний спосіб життя: пошук людей за біговими, вело або outdoor-інтересами. Ризикована для бренду Strava.</t>
         </is>
       </c>
       <c r="C27" s="142" t="n">
@@ -2077,27 +2035,25 @@
       </c>
       <c r="D27" s="61" t="inlineStr">
         <is>
-          <t>🚫 KILL — weak fit + crowded</t>
-        </is>
-      </c>
-      <c r="E27" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §2.D Fit weak (dilutes identity) · §2.C crowded.
-💬 МЕНТОР: (без коментарів)
-📊 АНАЛІТИКА: MyFitnessPal, Noom ($3.7B valuation) — winners, Strava late.
-🏁 КОНКУРЕНТИ: MyFitnessPal · Noom · Yazio · MacroFactor</t>
-        </is>
-      </c>
-      <c r="F27" s="144" t="inlineStr"/>
+          <t>🚫 KILL — ризик для core</t>
+        </is>
+      </c>
+      <c r="E27" s="163" t="inlineStr">
+        <is>
+          <t>🎓 §2.D Risk to core brand · §7 Avoid: not Strava DNA
+💬 Ментор: «Питання релевантності та конверсії»
+🏁 Bumble fitness mode — feature, не app</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="80" customHeight="1" s="23">
       <c r="A28" s="139" t="n">
         <v>21</v>
       </c>
-      <c r="B28" s="140" t="inlineStr">
+      <c r="B28" s="168" t="inlineStr">
         <is>
           <t>Youth Sports Logistics
-Дитячі/юнацькі команди</t>
+Інструменти для дитячих команд: розклади, батьки, тренери, відвідуваність, координація. Багато privacy і ops-ризиків.</t>
         </is>
       </c>
       <c r="C28" s="142" t="n">
@@ -2108,24 +2064,22 @@
           <t>🚫 KILL — мало грошей</t>
         </is>
       </c>
-      <c r="E28" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §2.A Small $ · §2.D Fit weak (Strava = adult athlete brand).
-💬 МЕНТОР: «Я би скіпав — виглядає як мало грошей.»
-📊 АНАЛІТИКА: TeamSnap 1.6M DL / $3.8M — entrenched incumbent.
-🏁 КОНКУРЕНТИ: TeamSnap · GameChanger · Spond · SportsEngine</t>
-        </is>
-      </c>
-      <c r="F28" s="144" t="inlineStr"/>
+      <c r="E28" s="163" t="inlineStr">
+        <is>
+          <t>🎓 §2.A Small $ · §2.D Fit weak (Strava = adult brand)
+💬 Ментор: «Виглядає як мало грошей — skip»
+🏁 TeamSnap entrenched · SportsEngine dominant</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="80" customHeight="1" s="23">
       <c r="A29" s="139" t="n">
         <v>22</v>
       </c>
-      <c r="B29" s="140" t="inlineStr">
+      <c r="B29" s="168" t="inlineStr">
         <is>
           <t>Strava Paws / Dog-Friendly Activities
-Власники собак</t>
+Шар для активностей із собакою: dog-friendly runs, community events і challenge-и для pet lifestyle + рухова активність.</t>
         </is>
       </c>
       <c r="C29" s="142" t="n">
@@ -2136,24 +2090,22 @@
           <t>🚫 KILL — нуль scale-apps</t>
         </is>
       </c>
-      <c r="E29" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §2.A niche · §2.D Fit weak.
-💬 МЕНТОР: «Треба оцінити який % бігунів мають собак і бігає з ними.»
-📊 АНАЛІТИКА: Нуль scale-apps у «dog-fitness» (negative signal).
-🏁 КОНКУРЕНТИ: Wag · Rover · Sniffspot · Dogo (limited direct)</t>
-        </is>
-      </c>
-      <c r="F29" s="144" t="inlineStr"/>
+      <c r="E29" s="163" t="inlineStr">
+        <is>
+          <t>🎓 §2.A niche · §2.D Fit weak
+💬 Ментор: «Оцінити % бігунів з собаками»
+📊 Нуль scale-apps у dog-fitness (negative signal)</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="80" customHeight="1" s="23">
       <c r="A30" s="139" t="n">
         <v>23</v>
       </c>
-      <c r="B30" s="140" t="inlineStr">
+      <c r="B30" s="168" t="inlineStr">
         <is>
           <t>Strava Virtual / AR Training
-Віртуальний/AR досвід</t>
+Віртуальні тренування або AR-досвід. Ефектно, але важко для MVP і слабко пов'язано з головною силою Strava.</t>
         </is>
       </c>
       <c r="C30" s="142" t="n">
@@ -2164,23 +2116,19 @@
           <t>🚫 KILL — Zwift домінує</t>
         </is>
       </c>
-      <c r="E30" s="125" t="inlineStr">
-        <is>
-          <t>🎓 GENESIS §2.C конкурент домінує · §2.D Proto Very hard (no 3D engine).
-💬 МЕНТОР: «Скіп.»
-📊 АНАЛІТИКА: Zwift $450M+ funding, $1B+ valuation — incumbent lock.
-🏁 КОНКУРЕНТИ: Zwift · ROUVY · TrainerRoad · MyWhoosh</t>
-        </is>
-      </c>
-      <c r="F30" s="144" t="inlineStr"/>
+      <c r="E30" s="163" t="inlineStr">
+        <is>
+          <t>🎓 §2.C конкурент домінує · §2.D Proto Very hard
+💬 Ментор: «Скіп»
+🏁 Zwift $1B+ valuation — incumbent lock</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2194,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="23" min="1" max="1"/>
@@ -2331,122 +2279,143 @@
       </c>
       <c r="B10" s="79" t="inlineStr">
         <is>
+          <t>Nutrition / Calorie Counter (AI-wave)</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="inlineStr">
+        <is>
+          <t>🟢 Найбільший за revenue, але fit під питанням</t>
+        </is>
+      </c>
+      <c r="D10" s="80" t="inlineStr">
+        <is>
+          <t>MyFitnessPal $382M · Cal AI +172% YoY</t>
+        </is>
+      </c>
+      <c r="E10" s="80" t="inlineStr">
+        <is>
+          <t>Найбільший revenue-кластер у датасеті ($833M, +17% YoY). AI-хвиля: Cal AI, Calo, BitePal. 💬 Ментор: «не викидати з шорт-ліста». Fit-питання відкрите.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1" s="23">
+      <c r="A11" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="79" t="inlineStr">
+        <is>
           <t>Strava Courts / Social Sports</t>
         </is>
       </c>
-      <c r="C10" s="53" t="inlineStr">
+      <c r="C11" s="53" t="inlineStr">
         <is>
           <t>🟢 Timely нішa</t>
         </is>
       </c>
-      <c r="D10" s="80" t="inlineStr">
+      <c r="D11" s="80" t="inlineStr">
         <is>
           <t>Playtomic 3.4M downloads</t>
         </is>
       </c>
-      <c r="E10" s="80" t="inlineStr">
+      <c r="E11" s="80" t="inlineStr">
         <is>
           <t>Менший ринок, але найшвидше зростання; сильний mentor-discussion кандидат.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1" s="23">
-      <c r="A11" s="59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B11" s="81" t="inlineStr">
+    <row r="12" ht="40" customHeight="1" s="23">
+      <c r="A12" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>Race / Event / Local Experiences</t>
         </is>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>🟡 Помірно</t>
         </is>
       </c>
-      <c r="D11" s="82" t="inlineStr">
+      <c r="D12" s="82" t="inlineStr">
         <is>
           <t>GetYourGuide 17.5M · Meetup $14M</t>
         </is>
       </c>
-      <c r="E11" s="82" t="inlineStr">
+      <c r="E12" s="82" t="inlineStr">
         <is>
           <t>Demand on discovery behavior — великий; мобільний revenue недооцінений.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1" s="23">
-      <c r="A12" s="59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B12" s="81" t="inlineStr">
+    <row r="13" ht="40" customHeight="1" s="23">
+      <c r="A13" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="81" t="inlineStr">
         <is>
           <t>Recovery / Longevity</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C13" s="59" t="inlineStr">
         <is>
           <t>🟡 Demand є, monetization складна</t>
         </is>
       </c>
-      <c r="D12" s="82" t="inlineStr">
+      <c r="D13" s="82" t="inlineStr">
         <is>
           <t>Oura 3.4M · WHOOP 2.7M</t>
         </is>
       </c>
-      <c r="E12" s="82" t="inlineStr">
+      <c r="E13" s="82" t="inlineStr">
         <is>
           <t>Hardware-led; працюватиме як premium-feature, а не standalone ринок.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1" s="23">
-      <c r="A13" s="61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B13" s="83" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="61" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="83" t="inlineStr">
         <is>
           <t>Corporate Wellness / Strava for Work</t>
         </is>
       </c>
-      <c r="C13" s="61" t="inlineStr">
+      <c r="C14" s="61" t="inlineStr">
         <is>
           <t>🔴 Цим датасетом не валідується</t>
         </is>
       </c>
-      <c r="D13" s="84" t="inlineStr">
+      <c r="D14" s="84" t="inlineStr">
         <is>
           <t>— (B2B не покритий)</t>
         </is>
       </c>
-      <c r="E13" s="84" t="inlineStr">
+      <c r="E14" s="84" t="inlineStr">
         <is>
           <t>Потрібні PitchBook / Crunchbase / CB Insights, НЕ app-store дані.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1" s="23">
-      <c r="A15" s="77" t="inlineStr">
+    <row r="15" ht="26" customHeight="1" s="23"/>
+    <row r="16" ht="50" customHeight="1" s="23">
+      <c r="A16" s="77" t="inlineStr">
         <is>
           <t>💡 Bottom Line</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="50" customHeight="1" s="23">
-      <c r="A16" s="85" t="inlineStr">
-        <is>
-          <t>Якщо команда хоче найчистішу consumer market validation — Active Travel / Escapes + Coaching / Guided Training — найсильніші data-backed ставки, а Strava Courts — найкраща non-obvious нішa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1" s="23">
-      <c r="A18" s="86" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="85" t="inlineStr">
+        <is>
+          <t>Якщо команда хоче найчистішу consumer market validation — Active Travel / Escapes + Coaching / Guided Training — найсильніші data-backed ставки, Strava Courts — найкраща non-obvious ніша. 💬 Ментор додав: Nutrition ($833M) не викидати з шорт-ліста — найбільший revenue-кластер у датасеті.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1" s="23"/>
+    <row r="19">
+      <c r="A19" s="86" t="inlineStr">
         <is>
           <t>⚠️  Ці дані показують де користувачі вже демонструють попит і willingness-to-pay. Вони НЕ замінюють стратегічне судження про те, де у Strava найкраще right-to-win.</t>
         </is>
@@ -2473,7 +2442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -2493,6 +2462,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1" s="23">
       <c r="A3" s="87" t="inlineStr">
         <is>
@@ -2500,6 +2470,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="34" customHeight="1" s="23">
       <c r="A5" s="78" t="inlineStr">
         <is>
@@ -2746,8 +2717,53 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="98" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="177" t="inlineStr">
+        <is>
+          <t>🟢 Nutrition / Calorie Counter</t>
+        </is>
+      </c>
+      <c r="B12" s="94" t="inlineStr">
+        <is>
+          <t>$301M</t>
+        </is>
+      </c>
+      <c r="C12" s="94" t="inlineStr">
+        <is>
+          <t>$714M</t>
+        </is>
+      </c>
+      <c r="D12" s="95" t="inlineStr">
+        <is>
+          <t>$833M</t>
+        </is>
+      </c>
+      <c r="E12" s="96" t="n">
+        <v>833.2</v>
+      </c>
+      <c r="F12" s="97" t="inlineStr">
+        <is>
+          <t>+137%</t>
+        </is>
+      </c>
+      <c r="G12" s="97" t="inlineStr">
+        <is>
+          <t>+16.7%</t>
+        </is>
+      </c>
+      <c r="H12" s="178" t="inlineStr">
+        <is>
+          <t>⚠️ DL-ДАНИХ НЕМАЄ — nutrition apps тільки у Revenue-файлах ментора.
+Колонки "DL" для цього рядка = Revenue ($M): $301M → $714M → $833M.
+Найбільший revenue-кластер у датасеті. AI-хвиля: Cal AI +172%, Calo +2850%, BitePal +897%.
+💬 Ментор: не викидати з шорт-ліста.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="98" t="inlineStr">
         <is>
           <t>Легенда: 🟢 сильно підтримано даними · 🟡 є нюанси · 🔴 не валідується цим пакетом</t>
         </is>
@@ -3658,6 +3674,3410 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J93"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" style="23" min="1" max="1"/>
+    <col width="12" customWidth="1" style="23" min="2" max="2"/>
+    <col width="12" customWidth="1" style="23" min="3" max="3"/>
+    <col width="12" customWidth="1" style="23" min="4" max="4"/>
+    <col width="10" customWidth="1" style="23" min="5" max="5"/>
+    <col width="11" customWidth="1" style="23" min="6" max="6"/>
+    <col width="11" customWidth="1" style="23" min="7" max="7"/>
+    <col width="11" customWidth="1" style="23" min="8" max="8"/>
+    <col width="10" customWidth="1" style="23" min="9" max="9"/>
+    <col width="50" customWidth="1" style="23" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="23">
+      <c r="A1" s="152" t="inlineStr">
+        <is>
+          <t>Apps Detail — Revenue &amp; Downloads по кластерах · 3 роки</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1" s="23">
+      <c r="A2" s="153" t="inlineStr">
+        <is>
+          <t>Джерело: платні CSV-файли ментора (Sensor Tower / data.ai). Revenue = App Store + Google Play. — означає відсутність у тому типі файлів.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="23">
+      <c r="A4" s="154" t="inlineStr">
+        <is>
+          <t>🟢 Outdoor / Active Travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="23">
+      <c r="A5" s="155" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="B5" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2023-24</t>
+        </is>
+      </c>
+      <c r="C5" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2024-25</t>
+        </is>
+      </c>
+      <c r="D5" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2025-26</t>
+        </is>
+      </c>
+      <c r="E5" s="155" t="inlineStr">
+        <is>
+          <t>YoY Rev</t>
+        </is>
+      </c>
+      <c r="F5" s="155" t="inlineStr">
+        <is>
+          <t>DL 2023-24</t>
+        </is>
+      </c>
+      <c r="G5" s="155" t="inlineStr">
+        <is>
+          <t>DL 2024-25</t>
+        </is>
+      </c>
+      <c r="H5" s="155" t="inlineStr">
+        <is>
+          <t>DL 2025-26</t>
+        </is>
+      </c>
+      <c r="I5" s="155" t="inlineStr">
+        <is>
+          <t>YoY DL</t>
+        </is>
+      </c>
+      <c r="J5" s="155" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1" s="23">
+      <c r="A6" s="156" t="inlineStr">
+        <is>
+          <t>AllTrails</t>
+        </is>
+      </c>
+      <c r="B6" s="157" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="C6" s="157" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="D6" s="157" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="E6" s="157" t="inlineStr">
+        <is>
+          <t>+8.2%</t>
+        </is>
+      </c>
+      <c r="F6" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="157" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1" s="23">
+      <c r="A7" s="156" t="inlineStr">
+        <is>
+          <t>komoot</t>
+        </is>
+      </c>
+      <c r="B7" s="157" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="C7" s="157" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="D7" s="157" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="E7" s="157" t="inlineStr">
+        <is>
+          <t>+32.6%</t>
+        </is>
+      </c>
+      <c r="F7" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="157" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16" customHeight="1" s="23">
+      <c r="A8" s="156" t="inlineStr">
+        <is>
+          <t>Wikiloc</t>
+        </is>
+      </c>
+      <c r="B8" s="157" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="C8" s="157" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="D8" s="157" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="E8" s="157" t="inlineStr">
+        <is>
+          <t>+23.7%</t>
+        </is>
+      </c>
+      <c r="F8" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="157" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1" s="23">
+      <c r="A9" s="156" t="inlineStr">
+        <is>
+          <t>Trailforks</t>
+        </is>
+      </c>
+      <c r="B9" s="157" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="C9" s="157" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="D9" s="157" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="E9" s="157" t="inlineStr">
+        <is>
+          <t>+1.3%</t>
+        </is>
+      </c>
+      <c r="F9" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="157" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1" s="23">
+      <c r="A10" s="156" t="inlineStr">
+        <is>
+          <t>Ride with GPS</t>
+        </is>
+      </c>
+      <c r="B10" s="157" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="C10" s="157" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="D10" s="157" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E10" s="157" t="inlineStr">
+        <is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+      <c r="F10" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="157" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1" s="23">
+      <c r="A11" s="156" t="inlineStr">
+        <is>
+          <t>Outdooractive</t>
+        </is>
+      </c>
+      <c r="B11" s="157" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="C11" s="157" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="D11" s="157" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="E11" s="157" t="inlineStr">
+        <is>
+          <t>+12.3%</t>
+        </is>
+      </c>
+      <c r="F11" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="157" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1" s="23">
+      <c r="A12" s="156" t="inlineStr">
+        <is>
+          <t>Bikemap</t>
+        </is>
+      </c>
+      <c r="B12" s="157" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C12" s="157" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D12" s="157" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E12" s="157" t="inlineStr">
+        <is>
+          <t>+5.4%</t>
+        </is>
+      </c>
+      <c r="F12" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="157" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1" s="23">
+      <c r="A13" s="156" t="inlineStr">
+        <is>
+          <t>Garmin Connect</t>
+        </is>
+      </c>
+      <c r="B13" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="157" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="G13" s="157" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="H13" s="157" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="I13" s="157" t="inlineStr">
+        <is>
+          <t>+20.9%</t>
+        </is>
+      </c>
+      <c r="J13" s="157" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="23">
+      <c r="A14" s="158" t="inlineStr">
+        <is>
+          <t>КЛАСТЕР TOTAL</t>
+        </is>
+      </c>
+      <c r="B14" s="159" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="C14" s="159" t="n">
+        <v>119.84</v>
+      </c>
+      <c r="D14" s="159" t="n">
+        <v>137.04</v>
+      </c>
+      <c r="E14" s="159" t="inlineStr">
+        <is>
+          <t>+14.3%</t>
+        </is>
+      </c>
+      <c r="F14" s="159" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="G14" s="159" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="H14" s="159" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="I14" s="159" t="inlineStr">
+        <is>
+          <t>+20.9%</t>
+        </is>
+      </c>
+      <c r="J14" s="159" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="23">
+      <c r="A16" s="154" t="inlineStr">
+        <is>
+          <t>🟢 Coaching / Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="23">
+      <c r="A17" s="155" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="B17" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2023-24</t>
+        </is>
+      </c>
+      <c r="C17" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2024-25</t>
+        </is>
+      </c>
+      <c r="D17" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2025-26</t>
+        </is>
+      </c>
+      <c r="E17" s="155" t="inlineStr">
+        <is>
+          <t>YoY Rev</t>
+        </is>
+      </c>
+      <c r="F17" s="155" t="inlineStr">
+        <is>
+          <t>DL 2023-24</t>
+        </is>
+      </c>
+      <c r="G17" s="155" t="inlineStr">
+        <is>
+          <t>DL 2024-25</t>
+        </is>
+      </c>
+      <c r="H17" s="155" t="inlineStr">
+        <is>
+          <t>DL 2025-26</t>
+        </is>
+      </c>
+      <c r="I17" s="155" t="inlineStr">
+        <is>
+          <t>YoY DL</t>
+        </is>
+      </c>
+      <c r="J17" s="155" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1" s="23">
+      <c r="A18" s="156" t="inlineStr">
+        <is>
+          <t>Runna</t>
+        </is>
+      </c>
+      <c r="B18" s="157" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="C18" s="157" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="D18" s="157" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="E18" s="157" t="inlineStr">
+        <is>
+          <t>+60.3%</t>
+        </is>
+      </c>
+      <c r="F18" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="157" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1" s="23">
+      <c r="A19" s="156" t="inlineStr">
+        <is>
+          <t>TrainingPeaks</t>
+        </is>
+      </c>
+      <c r="B19" s="157" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="C19" s="157" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="D19" s="157" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="E19" s="157" t="inlineStr">
+        <is>
+          <t>+19.2%</t>
+        </is>
+      </c>
+      <c r="F19" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="157" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1" s="23">
+      <c r="A20" s="156" t="inlineStr">
+        <is>
+          <t>GOWOD</t>
+        </is>
+      </c>
+      <c r="B20" s="157" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="C20" s="157" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="D20" s="157" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E20" s="157" t="inlineStr">
+        <is>
+          <t>+19.0%</t>
+        </is>
+      </c>
+      <c r="F20" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="157" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1" s="23">
+      <c r="A21" s="156" t="inlineStr">
+        <is>
+          <t>CoachNow</t>
+        </is>
+      </c>
+      <c r="B21" s="157" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C21" s="157" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D21" s="157" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E21" s="157" t="inlineStr">
+        <is>
+          <t>+18.3%</t>
+        </is>
+      </c>
+      <c r="F21" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="157" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1" s="23">
+      <c r="A22" s="156" t="inlineStr">
+        <is>
+          <t>Humango</t>
+        </is>
+      </c>
+      <c r="B22" s="157" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C22" s="157" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D22" s="157" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E22" s="157" t="inlineStr">
+        <is>
+          <t>+71.8%</t>
+        </is>
+      </c>
+      <c r="F22" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="157" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1" s="23">
+      <c r="A23" s="156" t="inlineStr">
+        <is>
+          <t>Playbook</t>
+        </is>
+      </c>
+      <c r="B23" s="157" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C23" s="157" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="D23" s="157" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E23" s="157" t="inlineStr">
+        <is>
+          <t>-57.2%</t>
+        </is>
+      </c>
+      <c r="F23" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="157" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1" s="23">
+      <c r="A24" s="156" t="inlineStr">
+        <is>
+          <t>LADDER Strength Training Plans</t>
+        </is>
+      </c>
+      <c r="B24" s="157" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="C24" s="157" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="D24" s="157" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="E24" s="157" t="inlineStr">
+        <is>
+          <t>-13.2%</t>
+        </is>
+      </c>
+      <c r="F24" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="157" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1" s="23">
+      <c r="A25" s="156" t="inlineStr">
+        <is>
+          <t>Peloton</t>
+        </is>
+      </c>
+      <c r="B25" s="157" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="C25" s="157" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="D25" s="157" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="E25" s="157" t="inlineStr">
+        <is>
+          <t>-55.3%</t>
+        </is>
+      </c>
+      <c r="F25" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="157" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1" s="23">
+      <c r="A26" s="156" t="inlineStr">
+        <is>
+          <t>Stryd</t>
+        </is>
+      </c>
+      <c r="B26" s="157" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C26" s="157" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D26" s="157" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E26" s="157" t="inlineStr">
+        <is>
+          <t>-22.0%</t>
+        </is>
+      </c>
+      <c r="F26" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="157" t="inlineStr"/>
+    </row>
+    <row r="27" ht="16" customHeight="1" s="23">
+      <c r="A27" s="156" t="inlineStr">
+        <is>
+          <t>Recover Athletics</t>
+        </is>
+      </c>
+      <c r="B27" s="157" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C27" s="157" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D27" s="157" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E27" s="157" t="inlineStr">
+        <is>
+          <t>-27.1%</t>
+        </is>
+      </c>
+      <c r="F27" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="157" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1" s="23">
+      <c r="A28" s="156" t="inlineStr">
+        <is>
+          <t>Final Surge</t>
+        </is>
+      </c>
+      <c r="B28" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="157" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D28" s="157" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E28" s="157" t="inlineStr">
+        <is>
+          <t>+67.3%</t>
+        </is>
+      </c>
+      <c r="F28" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="157" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1" s="23">
+      <c r="A29" s="156" t="inlineStr">
+        <is>
+          <t>Fitplan®</t>
+        </is>
+      </c>
+      <c r="B29" s="157" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C29" s="157" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D29" s="157" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E29" s="157" t="inlineStr">
+        <is>
+          <t>-77.2%</t>
+        </is>
+      </c>
+      <c r="F29" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="157" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="23">
+      <c r="A30" s="156" t="inlineStr">
+        <is>
+          <t>Physitrack</t>
+        </is>
+      </c>
+      <c r="B30" s="157" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C30" s="157" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D30" s="157" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E30" s="157" t="inlineStr">
+        <is>
+          <t>+27.4%</t>
+        </is>
+      </c>
+      <c r="F30" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="157" t="inlineStr"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="23">
+      <c r="A31" s="158" t="inlineStr">
+        <is>
+          <t>КЛАСТЕР TOTAL</t>
+        </is>
+      </c>
+      <c r="B31" s="159" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="C31" s="159" t="n">
+        <v>211.78</v>
+      </c>
+      <c r="D31" s="159" t="n">
+        <v>165.84</v>
+      </c>
+      <c r="E31" s="159" t="inlineStr">
+        <is>
+          <t>-21.7%</t>
+        </is>
+      </c>
+      <c r="F31" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="159" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="23">
+      <c r="A33" s="154" t="inlineStr">
+        <is>
+          <t>🟢 Nutrition / Calorie Counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="23">
+      <c r="A34" s="155" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="B34" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2023-24</t>
+        </is>
+      </c>
+      <c r="C34" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2024-25</t>
+        </is>
+      </c>
+      <c r="D34" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2025-26</t>
+        </is>
+      </c>
+      <c r="E34" s="155" t="inlineStr">
+        <is>
+          <t>YoY Rev</t>
+        </is>
+      </c>
+      <c r="F34" s="155" t="inlineStr">
+        <is>
+          <t>DL 2023-24</t>
+        </is>
+      </c>
+      <c r="G34" s="155" t="inlineStr">
+        <is>
+          <t>DL 2024-25</t>
+        </is>
+      </c>
+      <c r="H34" s="155" t="inlineStr">
+        <is>
+          <t>DL 2025-26</t>
+        </is>
+      </c>
+      <c r="I34" s="155" t="inlineStr">
+        <is>
+          <t>YoY DL</t>
+        </is>
+      </c>
+      <c r="J34" s="155" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1" s="23">
+      <c r="A35" s="156" t="inlineStr">
+        <is>
+          <t>MyFitnessPal</t>
+        </is>
+      </c>
+      <c r="B35" s="157" t="n">
+        <v>185.49</v>
+      </c>
+      <c r="C35" s="157" t="n">
+        <v>389.61</v>
+      </c>
+      <c r="D35" s="157" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="E35" s="157" t="inlineStr">
+        <is>
+          <t>-2.0%</t>
+        </is>
+      </c>
+      <c r="F35" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="157" t="inlineStr"/>
+    </row>
+    <row r="36" ht="16" customHeight="1" s="23">
+      <c r="A36" s="156" t="inlineStr">
+        <is>
+          <t>AI Calorie Tracker by Yazio</t>
+        </is>
+      </c>
+      <c r="B36" s="157" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="C36" s="157" t="n">
+        <v>98.37</v>
+      </c>
+      <c r="D36" s="157" t="n">
+        <v>130.86</v>
+      </c>
+      <c r="E36" s="157" t="inlineStr">
+        <is>
+          <t>+33.0%</t>
+        </is>
+      </c>
+      <c r="F36" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="157" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1" s="23">
+      <c r="A37" s="156" t="inlineStr">
+        <is>
+          <t>Cal AI</t>
+        </is>
+      </c>
+      <c r="B37" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="157" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="D37" s="157" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="E37" s="157" t="inlineStr">
+        <is>
+          <t>+171.5%</t>
+        </is>
+      </c>
+      <c r="F37" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="157" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1" s="23">
+      <c r="A38" s="156" t="inlineStr">
+        <is>
+          <t>Lose It!</t>
+        </is>
+      </c>
+      <c r="B38" s="157" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="C38" s="157" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="D38" s="157" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="E38" s="157" t="inlineStr">
+        <is>
+          <t>-23.3%</t>
+        </is>
+      </c>
+      <c r="F38" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="157" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1" s="23">
+      <c r="A39" s="156" t="inlineStr">
+        <is>
+          <t>Foodvisor</t>
+        </is>
+      </c>
+      <c r="B39" s="157" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C39" s="157" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="D39" s="157" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="E39" s="157" t="inlineStr">
+        <is>
+          <t>+50.9%</t>
+        </is>
+      </c>
+      <c r="F39" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="157" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1" s="23">
+      <c r="A40" s="156" t="inlineStr">
+        <is>
+          <t>Calorie Counter +</t>
+        </is>
+      </c>
+      <c r="B40" s="157" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="C40" s="157" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="D40" s="157" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="E40" s="157" t="inlineStr">
+        <is>
+          <t>+2.8%</t>
+        </is>
+      </c>
+      <c r="F40" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="157" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1" s="23">
+      <c r="A41" s="156" t="inlineStr">
+        <is>
+          <t>Calorie Counter</t>
+        </is>
+      </c>
+      <c r="B41" s="157" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="C41" s="157" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="D41" s="157" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="E41" s="157" t="inlineStr">
+        <is>
+          <t>+64.4%</t>
+        </is>
+      </c>
+      <c r="F41" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="157" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1" s="23">
+      <c r="A42" s="156" t="inlineStr">
+        <is>
+          <t>BitePal</t>
+        </is>
+      </c>
+      <c r="B42" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C42" s="157" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D42" s="157" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="E42" s="157" t="inlineStr">
+        <is>
+          <t>+896.6%</t>
+        </is>
+      </c>
+      <c r="F42" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="157" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1" s="23">
+      <c r="A43" s="156" t="inlineStr">
+        <is>
+          <t>Noom Weight Loss, Food Tracker</t>
+        </is>
+      </c>
+      <c r="B43" s="157" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="C43" s="157" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D43" s="157" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="E43" s="157" t="inlineStr">
+        <is>
+          <t>-12.4%</t>
+        </is>
+      </c>
+      <c r="F43" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="157" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1" s="23">
+      <c r="A44" s="156" t="inlineStr">
+        <is>
+          <t>Cronometer</t>
+        </is>
+      </c>
+      <c r="B44" s="157" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="C44" s="157" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="D44" s="157" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="E44" s="157" t="inlineStr">
+        <is>
+          <t>+60.6%</t>
+        </is>
+      </c>
+      <c r="F44" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="157" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1" s="23">
+      <c r="A45" s="156" t="inlineStr">
+        <is>
+          <t>Calorie Counter &amp; Food Tracker</t>
+        </is>
+      </c>
+      <c r="B45" s="157" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C45" s="157" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="D45" s="157" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="E45" s="157" t="inlineStr">
+        <is>
+          <t>+289.5%</t>
+        </is>
+      </c>
+      <c r="F45" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="157" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1" s="23">
+      <c r="A46" s="156" t="inlineStr">
+        <is>
+          <t>Calo</t>
+        </is>
+      </c>
+      <c r="B46" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="157" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D46" s="157" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="E46" s="157" t="inlineStr">
+        <is>
+          <t>+2850.2%</t>
+        </is>
+      </c>
+      <c r="F46" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="157" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1" s="23">
+      <c r="A47" s="156" t="inlineStr">
+        <is>
+          <t>Fitia</t>
+        </is>
+      </c>
+      <c r="B47" s="157" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C47" s="157" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="D47" s="157" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="E47" s="157" t="inlineStr">
+        <is>
+          <t>+66.2%</t>
+        </is>
+      </c>
+      <c r="F47" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="157" t="inlineStr"/>
+    </row>
+    <row r="48" ht="18" customHeight="1" s="23">
+      <c r="A48" s="158" t="inlineStr">
+        <is>
+          <t>КЛАСТЕР TOTAL</t>
+        </is>
+      </c>
+      <c r="B48" s="159" t="n">
+        <v>301.13</v>
+      </c>
+      <c r="C48" s="159" t="n">
+        <v>714</v>
+      </c>
+      <c r="D48" s="159" t="n">
+        <v>833.23</v>
+      </c>
+      <c r="E48" s="159" t="inlineStr">
+        <is>
+          <t>+16.7%</t>
+        </is>
+      </c>
+      <c r="F48" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="159" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1" s="23">
+      <c r="A50" s="154" t="inlineStr">
+        <is>
+          <t>🟡 Events / Travel Discovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="23">
+      <c r="A51" s="155" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="B51" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2023-24</t>
+        </is>
+      </c>
+      <c r="C51" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2024-25</t>
+        </is>
+      </c>
+      <c r="D51" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2025-26</t>
+        </is>
+      </c>
+      <c r="E51" s="155" t="inlineStr">
+        <is>
+          <t>YoY Rev</t>
+        </is>
+      </c>
+      <c r="F51" s="155" t="inlineStr">
+        <is>
+          <t>DL 2023-24</t>
+        </is>
+      </c>
+      <c r="G51" s="155" t="inlineStr">
+        <is>
+          <t>DL 2024-25</t>
+        </is>
+      </c>
+      <c r="H51" s="155" t="inlineStr">
+        <is>
+          <t>DL 2025-26</t>
+        </is>
+      </c>
+      <c r="I51" s="155" t="inlineStr">
+        <is>
+          <t>YoY DL</t>
+        </is>
+      </c>
+      <c r="J51" s="155" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1" s="23">
+      <c r="A52" s="156" t="inlineStr">
+        <is>
+          <t>GetYourGuide</t>
+        </is>
+      </c>
+      <c r="B52" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C52" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="157" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="G52" s="157" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="H52" s="157" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="I52" s="157" t="inlineStr">
+        <is>
+          <t>-45.0%</t>
+        </is>
+      </c>
+      <c r="J52" s="157" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1" s="23">
+      <c r="A53" s="156" t="inlineStr">
+        <is>
+          <t>Fever</t>
+        </is>
+      </c>
+      <c r="B53" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C53" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D53" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="157" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="G53" s="157" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="H53" s="157" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I53" s="157" t="inlineStr">
+        <is>
+          <t>-33.4%</t>
+        </is>
+      </c>
+      <c r="J53" s="157" t="inlineStr"/>
+    </row>
+    <row r="54" ht="16" customHeight="1" s="23">
+      <c r="A54" s="156" t="inlineStr">
+        <is>
+          <t>Eventbrite</t>
+        </is>
+      </c>
+      <c r="B54" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C54" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="157" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="G54" s="157" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="H54" s="157" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="I54" s="157" t="inlineStr">
+        <is>
+          <t>-67.9%</t>
+        </is>
+      </c>
+      <c r="J54" s="157" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1" s="23">
+      <c r="A55" s="156" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="B55" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C55" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D55" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="157" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="G55" s="157" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="H55" s="157" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I55" s="157" t="inlineStr">
+        <is>
+          <t>-36.4%</t>
+        </is>
+      </c>
+      <c r="J55" s="157" t="inlineStr"/>
+    </row>
+    <row r="56" ht="16" customHeight="1" s="23">
+      <c r="A56" s="156" t="inlineStr">
+        <is>
+          <t>Viator Tours &amp; Attractions</t>
+        </is>
+      </c>
+      <c r="B56" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C56" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="157" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G56" s="157" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="H56" s="157" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="I56" s="157" t="inlineStr">
+        <is>
+          <t>-57.0%</t>
+        </is>
+      </c>
+      <c r="J56" s="157" t="inlineStr"/>
+    </row>
+    <row r="57" ht="16" customHeight="1" s="23">
+      <c r="A57" s="156" t="inlineStr">
+        <is>
+          <t>ClassPass</t>
+        </is>
+      </c>
+      <c r="B57" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C57" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="157" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G57" s="157" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="H57" s="157" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="I57" s="157" t="inlineStr">
+        <is>
+          <t>-43.1%</t>
+        </is>
+      </c>
+      <c r="J57" s="157" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1" s="23">
+      <c r="A58" s="156" t="inlineStr">
+        <is>
+          <t>Timeleft</t>
+        </is>
+      </c>
+      <c r="B58" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C58" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="157" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G58" s="157" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="H58" s="157" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I58" s="157" t="inlineStr">
+        <is>
+          <t>-53.0%</t>
+        </is>
+      </c>
+      <c r="J58" s="157" t="inlineStr"/>
+    </row>
+    <row r="59" ht="18" customHeight="1" s="23">
+      <c r="A59" s="160" t="inlineStr">
+        <is>
+          <t>КЛАСТЕР TOTAL</t>
+        </is>
+      </c>
+      <c r="B59" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C59" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D59" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="161" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="G59" s="161" t="n">
+        <v>106.83</v>
+      </c>
+      <c r="H59" s="161" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="I59" s="161" t="inlineStr">
+        <is>
+          <t>-49.9%</t>
+        </is>
+      </c>
+      <c r="J59" s="161" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1" s="23">
+      <c r="A61" s="154" t="inlineStr">
+        <is>
+          <t>🟢 Social Sports / Courts</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1" s="23">
+      <c r="A62" s="155" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="B62" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2023-24</t>
+        </is>
+      </c>
+      <c r="C62" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2024-25</t>
+        </is>
+      </c>
+      <c r="D62" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2025-26</t>
+        </is>
+      </c>
+      <c r="E62" s="155" t="inlineStr">
+        <is>
+          <t>YoY Rev</t>
+        </is>
+      </c>
+      <c r="F62" s="155" t="inlineStr">
+        <is>
+          <t>DL 2023-24</t>
+        </is>
+      </c>
+      <c r="G62" s="155" t="inlineStr">
+        <is>
+          <t>DL 2024-25</t>
+        </is>
+      </c>
+      <c r="H62" s="155" t="inlineStr">
+        <is>
+          <t>DL 2025-26</t>
+        </is>
+      </c>
+      <c r="I62" s="155" t="inlineStr">
+        <is>
+          <t>YoY DL</t>
+        </is>
+      </c>
+      <c r="J62" s="155" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1" s="23">
+      <c r="A63" s="156" t="inlineStr">
+        <is>
+          <t>Playtomic</t>
+        </is>
+      </c>
+      <c r="B63" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C63" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D63" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="157" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G63" s="157" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H63" s="157" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="I63" s="157" t="inlineStr">
+        <is>
+          <t>+27.5%</t>
+        </is>
+      </c>
+      <c r="J63" s="157" t="inlineStr"/>
+    </row>
+    <row r="64" ht="16" customHeight="1" s="23">
+      <c r="A64" s="156" t="inlineStr">
+        <is>
+          <t>CourtReserve</t>
+        </is>
+      </c>
+      <c r="B64" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C64" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D64" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="157" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G64" s="157" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H64" s="157" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I64" s="157" t="inlineStr">
+        <is>
+          <t>+11.3%</t>
+        </is>
+      </c>
+      <c r="J64" s="157" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1" s="23">
+      <c r="A65" s="156" t="inlineStr">
+        <is>
+          <t>MATCHi</t>
+        </is>
+      </c>
+      <c r="B65" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C65" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D65" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="157" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G65" s="157" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H65" s="157" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I65" s="157" t="inlineStr">
+        <is>
+          <t>+2.6%</t>
+        </is>
+      </c>
+      <c r="J65" s="157" t="inlineStr"/>
+    </row>
+    <row r="66" ht="16" customHeight="1" s="23">
+      <c r="A66" s="156" t="inlineStr">
+        <is>
+          <t>Pickleheads</t>
+        </is>
+      </c>
+      <c r="B66" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C66" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D66" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="157" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G66" s="157" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H66" s="157" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I66" s="157" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+      <c r="J66" s="157" t="inlineStr"/>
+    </row>
+    <row r="67" ht="16" customHeight="1" s="23">
+      <c r="A67" s="156" t="inlineStr">
+        <is>
+          <t>PlayYourCourt</t>
+        </is>
+      </c>
+      <c r="B67" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C67" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D67" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="157" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G67" s="157" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H67" s="157" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I67" s="157" t="inlineStr">
+        <is>
+          <t>-69.2%</t>
+        </is>
+      </c>
+      <c r="J67" s="157" t="inlineStr"/>
+    </row>
+    <row r="68" ht="16" customHeight="1" s="23">
+      <c r="A68" s="156" t="inlineStr">
+        <is>
+          <t>OpenSports</t>
+        </is>
+      </c>
+      <c r="B68" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C68" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="157" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G68" s="157" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H68" s="157" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I68" s="157" t="inlineStr">
+        <is>
+          <t>+40.3%</t>
+        </is>
+      </c>
+      <c r="J68" s="157" t="inlineStr"/>
+    </row>
+    <row r="69" ht="16" customHeight="1" s="23">
+      <c r="A69" s="156" t="inlineStr">
+        <is>
+          <t>Padel Club</t>
+        </is>
+      </c>
+      <c r="B69" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C69" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="157" t="inlineStr">
+        <is>
+          <t>+311.9%</t>
+        </is>
+      </c>
+      <c r="J69" s="157" t="inlineStr"/>
+    </row>
+    <row r="70" ht="16" customHeight="1" s="23">
+      <c r="A70" s="156" t="inlineStr">
+        <is>
+          <t>Skedda</t>
+        </is>
+      </c>
+      <c r="B70" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C70" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="157" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G70" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="157" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+      <c r="J70" s="157" t="inlineStr"/>
+    </row>
+    <row r="71" ht="18" customHeight="1" s="23">
+      <c r="A71" s="158" t="inlineStr">
+        <is>
+          <t>КЛАСТЕР TOTAL</t>
+        </is>
+      </c>
+      <c r="B71" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C71" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="159" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G71" s="159" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="H71" s="159" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="I71" s="159" t="inlineStr">
+        <is>
+          <t>+22.2%</t>
+        </is>
+      </c>
+      <c r="J71" s="159" t="inlineStr"/>
+    </row>
+    <row r="73" ht="20" customHeight="1" s="23">
+      <c r="A73" s="154" t="inlineStr">
+        <is>
+          <t>🟡 Recovery / Longevity</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1" s="23">
+      <c r="A74" s="155" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="B74" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2023-24</t>
+        </is>
+      </c>
+      <c r="C74" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2024-25</t>
+        </is>
+      </c>
+      <c r="D74" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2025-26</t>
+        </is>
+      </c>
+      <c r="E74" s="155" t="inlineStr">
+        <is>
+          <t>YoY Rev</t>
+        </is>
+      </c>
+      <c r="F74" s="155" t="inlineStr">
+        <is>
+          <t>DL 2023-24</t>
+        </is>
+      </c>
+      <c r="G74" s="155" t="inlineStr">
+        <is>
+          <t>DL 2024-25</t>
+        </is>
+      </c>
+      <c r="H74" s="155" t="inlineStr">
+        <is>
+          <t>DL 2025-26</t>
+        </is>
+      </c>
+      <c r="I74" s="155" t="inlineStr">
+        <is>
+          <t>YoY DL</t>
+        </is>
+      </c>
+      <c r="J74" s="155" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1" s="23">
+      <c r="A75" s="156" t="inlineStr">
+        <is>
+          <t>Oura</t>
+        </is>
+      </c>
+      <c r="B75" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C75" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="157" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G75" s="157" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H75" s="157" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I75" s="157" t="inlineStr">
+        <is>
+          <t>+93.1%</t>
+        </is>
+      </c>
+      <c r="J75" s="157" t="inlineStr"/>
+    </row>
+    <row r="76" ht="16" customHeight="1" s="23">
+      <c r="A76" s="156" t="inlineStr">
+        <is>
+          <t>WHOOP</t>
+        </is>
+      </c>
+      <c r="B76" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C76" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="157" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G76" s="157" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H76" s="157" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I76" s="157" t="inlineStr">
+        <is>
+          <t>+79.2%</t>
+        </is>
+      </c>
+      <c r="J76" s="157" t="inlineStr"/>
+    </row>
+    <row r="77" ht="16" customHeight="1" s="23">
+      <c r="A77" s="156" t="inlineStr">
+        <is>
+          <t>Eight Sleep</t>
+        </is>
+      </c>
+      <c r="B77" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C77" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="157" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G77" s="157" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H77" s="157" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I77" s="157" t="inlineStr">
+        <is>
+          <t>+29.9%</t>
+        </is>
+      </c>
+      <c r="J77" s="157" t="inlineStr"/>
+    </row>
+    <row r="78" ht="16" customHeight="1" s="23">
+      <c r="A78" s="156" t="inlineStr">
+        <is>
+          <t>HRV4Training</t>
+        </is>
+      </c>
+      <c r="B78" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C78" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="157" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G78" s="157" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H78" s="157" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I78" s="157" t="inlineStr">
+        <is>
+          <t>+9.4%</t>
+        </is>
+      </c>
+      <c r="J78" s="157" t="inlineStr"/>
+    </row>
+    <row r="79" ht="16" customHeight="1" s="23">
+      <c r="A79" s="156" t="inlineStr">
+        <is>
+          <t>Biostrap</t>
+        </is>
+      </c>
+      <c r="B79" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C79" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="157" t="inlineStr">
+        <is>
+          <t>-88.1%</t>
+        </is>
+      </c>
+      <c r="J79" s="157" t="inlineStr"/>
+    </row>
+    <row r="80" ht="16" customHeight="1" s="23">
+      <c r="A80" s="156" t="inlineStr">
+        <is>
+          <t>Polar Flow</t>
+        </is>
+      </c>
+      <c r="B80" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C80" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="157" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G80" s="157" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H80" s="157" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I80" s="157" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="J80" s="157" t="inlineStr"/>
+    </row>
+    <row r="81" ht="18" customHeight="1" s="23">
+      <c r="A81" s="160" t="inlineStr">
+        <is>
+          <t>КЛАСТЕР TOTAL</t>
+        </is>
+      </c>
+      <c r="B81" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C81" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="161" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G81" s="161" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H81" s="161" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="I81" s="161" t="inlineStr">
+        <is>
+          <t>+66.0%</t>
+        </is>
+      </c>
+      <c r="J81" s="161" t="inlineStr"/>
+    </row>
+    <row r="83" ht="20" customHeight="1" s="23">
+      <c r="A83" s="154" t="inlineStr">
+        <is>
+          <t>🟡 Community / Team Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1" s="23">
+      <c r="A84" s="155" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="B84" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2023-24</t>
+        </is>
+      </c>
+      <c r="C84" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2024-25</t>
+        </is>
+      </c>
+      <c r="D84" s="155" t="inlineStr">
+        <is>
+          <t>Rev 2025-26</t>
+        </is>
+      </c>
+      <c r="E84" s="155" t="inlineStr">
+        <is>
+          <t>YoY Rev</t>
+        </is>
+      </c>
+      <c r="F84" s="155" t="inlineStr">
+        <is>
+          <t>DL 2023-24</t>
+        </is>
+      </c>
+      <c r="G84" s="155" t="inlineStr">
+        <is>
+          <t>DL 2024-25</t>
+        </is>
+      </c>
+      <c r="H84" s="155" t="inlineStr">
+        <is>
+          <t>DL 2025-26</t>
+        </is>
+      </c>
+      <c r="I84" s="155" t="inlineStr">
+        <is>
+          <t>YoY DL</t>
+        </is>
+      </c>
+      <c r="J84" s="155" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1" s="23">
+      <c r="A85" s="156" t="inlineStr">
+        <is>
+          <t>GroupMe</t>
+        </is>
+      </c>
+      <c r="B85" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C85" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D85" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="157" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="G85" s="157" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="H85" s="157" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I85" s="157" t="inlineStr">
+        <is>
+          <t>+6.4%</t>
+        </is>
+      </c>
+      <c r="J85" s="157" t="inlineStr"/>
+    </row>
+    <row r="86" ht="16" customHeight="1" s="23">
+      <c r="A86" s="156" t="inlineStr">
+        <is>
+          <t>Spond</t>
+        </is>
+      </c>
+      <c r="B86" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C86" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D86" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="157" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G86" s="157" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H86" s="157" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I86" s="157" t="inlineStr">
+        <is>
+          <t>+8.9%</t>
+        </is>
+      </c>
+      <c r="J86" s="157" t="inlineStr"/>
+    </row>
+    <row r="87" ht="16" customHeight="1" s="23">
+      <c r="A87" s="156" t="inlineStr">
+        <is>
+          <t>TeamSnap</t>
+        </is>
+      </c>
+      <c r="B87" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C87" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D87" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="157" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G87" s="157" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H87" s="157" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I87" s="157" t="inlineStr">
+        <is>
+          <t>-19.4%</t>
+        </is>
+      </c>
+      <c r="J87" s="157" t="inlineStr"/>
+    </row>
+    <row r="88" ht="16" customHeight="1" s="23">
+      <c r="A88" s="156" t="inlineStr">
+        <is>
+          <t>SportsEngine</t>
+        </is>
+      </c>
+      <c r="B88" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C88" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D88" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="157" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G88" s="157" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H88" s="157" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I88" s="157" t="inlineStr">
+        <is>
+          <t>-9.0%</t>
+        </is>
+      </c>
+      <c r="J88" s="157" t="inlineStr"/>
+    </row>
+    <row r="89" ht="16" customHeight="1" s="23">
+      <c r="A89" s="156" t="inlineStr">
+        <is>
+          <t>Heja</t>
+        </is>
+      </c>
+      <c r="B89" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C89" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D89" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E89" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="157" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G89" s="157" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H89" s="157" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I89" s="157" t="inlineStr">
+        <is>
+          <t>-14.5%</t>
+        </is>
+      </c>
+      <c r="J89" s="157" t="inlineStr"/>
+    </row>
+    <row r="90" ht="16" customHeight="1" s="23">
+      <c r="A90" s="156" t="inlineStr">
+        <is>
+          <t>Stack Team App</t>
+        </is>
+      </c>
+      <c r="B90" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C90" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D90" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="157" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G90" s="157" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H90" s="157" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I90" s="157" t="inlineStr">
+        <is>
+          <t>-19.5%</t>
+        </is>
+      </c>
+      <c r="J90" s="157" t="inlineStr"/>
+    </row>
+    <row r="91" ht="16" customHeight="1" s="23">
+      <c r="A91" s="156" t="inlineStr">
+        <is>
+          <t>SportsEngine Tourney</t>
+        </is>
+      </c>
+      <c r="B91" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C91" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D91" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="157" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G91" s="157" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H91" s="157" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I91" s="157" t="inlineStr">
+        <is>
+          <t>-10.0%</t>
+        </is>
+      </c>
+      <c r="J91" s="157" t="inlineStr"/>
+    </row>
+    <row r="92" ht="16" customHeight="1" s="23">
+      <c r="A92" s="156" t="inlineStr">
+        <is>
+          <t>LeagueApps Play</t>
+        </is>
+      </c>
+      <c r="B92" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C92" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D92" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="157" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G92" s="157" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H92" s="157" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I92" s="157" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="J92" s="157" t="inlineStr"/>
+    </row>
+    <row r="93" ht="18" customHeight="1" s="23">
+      <c r="A93" s="160" t="inlineStr">
+        <is>
+          <t>КЛАСТЕР TOTAL</t>
+        </is>
+      </c>
+      <c r="B93" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C93" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D93" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="161" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="G93" s="161" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="H93" s="161" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="I93" s="161" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="J93" s="161" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A83:J83"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A33:J33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3876,7 +7296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="00548235"/>
@@ -5973,7 +9393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="007F7F7F"/>
